--- a/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
@@ -1257,7 +1257,7 @@
         <v>5000</v>
       </c>
       <c r="F20" s="3">
-        <v>-25200</v>
+        <v>5500</v>
       </c>
       <c r="G20" s="3">
         <v>9000</v>
@@ -1308,7 +1308,7 @@
         <v>2164700</v>
       </c>
       <c r="F21" s="3">
-        <v>2106400</v>
+        <v>2075700</v>
       </c>
       <c r="G21" s="3">
         <v>1853600</v>
@@ -1869,7 +1869,7 @@
         <v>-5000</v>
       </c>
       <c r="F32" s="3">
-        <v>25200</v>
+        <v>-5500</v>
       </c>
       <c r="G32" s="3">
         <v>-9000</v>
